--- a/artfynd/A 18100-2022 artfynd.xlsx
+++ b/artfynd/A 18100-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18100-2022 artfynd.xlsx
+++ b/artfynd/A 18100-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109341447</v>
+        <v>109340373</v>
       </c>
       <c r="B2" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,18 +703,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djurgården, Srm</t>
+          <t>Bocksjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666860.410359901</v>
+        <v>666793</v>
       </c>
       <c r="R2" t="n">
-        <v>6561992.904399308</v>
+        <v>6561950</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +793,238 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109341447</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djurgården, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>666860</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6561993</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Doina Velasquez</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Doina Velasquez</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109341556</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bocksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>666840</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6561971</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Doina Velasquez</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Doina Velasquez</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18100-2022 artfynd.xlsx
+++ b/artfynd/A 18100-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109340373</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109341447</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,8 +1040,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109341556</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>